--- a/BVSimulationFiles/86.xlsx
+++ b/BVSimulationFiles/86.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006784565916398713</v>
+        <v>0.001356913183279743</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006909798612286343</v>
+        <v>0.001381959722457269</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007035031308173972</v>
+        <v>0.001407006261634794</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007160264004061601</v>
+        <v>0.00143205280081232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007285496699949229</v>
+        <v>0.001457099339989846</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007410729395836859</v>
+        <v>0.001482145879167372</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007535962091724486</v>
+        <v>0.001507192418344897</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007661194787612117</v>
+        <v>0.001532238957522423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007786427483499746</v>
+        <v>0.001557285496699949</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0007911660179387376</v>
+        <v>0.001582332035877475</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008036892875275005</v>
+        <v>0.001607378575055001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008162125571162634</v>
+        <v>0.001632425114232527</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008287358267050263</v>
+        <v>0.001657471653410053</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000841259096293789</v>
+        <v>0.001682518192587578</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0008537823658825522</v>
+        <v>0.001707564731765104</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000866305635471315</v>
+        <v>0.00173261127094263</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000878828905060078</v>
+        <v>0.001757657810120156</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008913521746488407</v>
+        <v>0.001782704349297681</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0009038754442376038</v>
+        <v>0.001807750888475208</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0009163987138263665</v>
+        <v>0.001832797427652733</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0006784565916398713</v>
+        <v>0.001356913183279743</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006909798612286343</v>
+        <v>0.001381959722457269</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007035031308173972</v>
+        <v>0.001407006261634794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007160264004061601</v>
+        <v>0.00143205280081232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007285496699949229</v>
+        <v>0.001457099339989846</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007410729395836859</v>
+        <v>0.001482145879167372</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007535962091724486</v>
+        <v>0.001507192418344897</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007661194787612117</v>
+        <v>0.001532238957522423</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007786427483499746</v>
+        <v>0.001557285496699949</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007911660179387376</v>
+        <v>0.001582332035877475</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008036892875275005</v>
+        <v>0.001607378575055001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008162125571162634</v>
+        <v>0.001632425114232527</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008287358267050263</v>
+        <v>0.001657471653410053</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000841259096293789</v>
+        <v>0.001682518192587578</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0008537823658825522</v>
+        <v>0.001707564731765104</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000866305635471315</v>
+        <v>0.00173261127094263</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000878828905060078</v>
+        <v>0.001757657810120156</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0008913521746488407</v>
+        <v>0.001782704349297681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0009038754442376038</v>
+        <v>0.001807750888475208</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009163987138263665</v>
+        <v>0.001832797427652733</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/86.xlsx
+++ b/BVSimulationFiles/86.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001356913183279743</v>
+        <v>0.01356913183279743</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001381959722457269</v>
+        <v>0.01381959722457269</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001407006261634794</v>
+        <v>0.01407006261634794</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00143205280081232</v>
+        <v>0.0143205280081232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001457099339989846</v>
+        <v>0.01457099339989846</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001482145879167372</v>
+        <v>0.01482145879167372</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001507192418344897</v>
+        <v>0.01507192418344897</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001532238957522423</v>
+        <v>0.01532238957522423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001557285496699949</v>
+        <v>0.01557285496699949</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001582332035877475</v>
+        <v>0.01582332035877475</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001607378575055001</v>
+        <v>0.01607378575055001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001632425114232527</v>
+        <v>0.01632425114232527</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001657471653410053</v>
+        <v>0.01657471653410053</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001682518192587578</v>
+        <v>0.01682518192587578</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001707564731765104</v>
+        <v>0.01707564731765104</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00173261127094263</v>
+        <v>0.0173261127094263</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001757657810120156</v>
+        <v>0.01757657810120156</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001782704349297681</v>
+        <v>0.01782704349297681</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001807750888475208</v>
+        <v>0.01807750888475208</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001832797427652733</v>
+        <v>0.01832797427652733</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001356913183279743</v>
+        <v>0.01356913183279743</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001381959722457269</v>
+        <v>0.01381959722457269</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001407006261634794</v>
+        <v>0.01407006261634794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00143205280081232</v>
+        <v>0.0143205280081232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001457099339989846</v>
+        <v>0.01457099339989846</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001482145879167372</v>
+        <v>0.01482145879167372</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001507192418344897</v>
+        <v>0.01507192418344897</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001532238957522423</v>
+        <v>0.01532238957522423</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001557285496699949</v>
+        <v>0.01557285496699949</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001582332035877475</v>
+        <v>0.01582332035877475</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001607378575055001</v>
+        <v>0.01607378575055001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001632425114232527</v>
+        <v>0.01632425114232527</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001657471653410053</v>
+        <v>0.01657471653410053</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001682518192587578</v>
+        <v>0.01682518192587578</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001707564731765104</v>
+        <v>0.01707564731765104</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00173261127094263</v>
+        <v>0.0173261127094263</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001757657810120156</v>
+        <v>0.01757657810120156</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001782704349297681</v>
+        <v>0.01782704349297681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001807750888475208</v>
+        <v>0.01807750888475208</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001832797427652733</v>
+        <v>0.01832797427652733</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/86.xlsx
+++ b/BVSimulationFiles/86.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.003382105263157895</v>
+        <v>0.002215862068965517</v>
       </c>
       <c r="D1" t="n">
-        <v>0.006764210526315789</v>
+        <v>0.004431724137931034</v>
       </c>
       <c r="E1" t="n">
-        <v>0.01014631578947368</v>
+        <v>0.006647586206896552</v>
       </c>
       <c r="F1" t="n">
-        <v>0.01352842105263158</v>
+        <v>0.008863448275862069</v>
       </c>
       <c r="G1" t="n">
-        <v>0.01691052631578947</v>
+        <v>0.01107931034482759</v>
       </c>
       <c r="H1" t="n">
-        <v>0.02029263157894737</v>
+        <v>0.0132951724137931</v>
       </c>
       <c r="I1" t="n">
-        <v>0.02367473684210526</v>
+        <v>0.01551103448275862</v>
       </c>
       <c r="J1" t="n">
-        <v>0.02705684210526316</v>
+        <v>0.01772689655172414</v>
       </c>
       <c r="K1" t="n">
-        <v>0.03043894736842105</v>
+        <v>0.01994275862068966</v>
       </c>
       <c r="L1" t="n">
-        <v>0.03382105263157895</v>
+        <v>0.02215862068965517</v>
       </c>
       <c r="M1" t="n">
-        <v>0.03720315789473684</v>
+        <v>0.02437448275862069</v>
       </c>
       <c r="N1" t="n">
-        <v>0.04058526315789474</v>
+        <v>0.02659034482758621</v>
       </c>
       <c r="O1" t="n">
-        <v>0.04396736842105262</v>
+        <v>0.02880620689655173</v>
       </c>
       <c r="P1" t="n">
-        <v>0.04734947368421052</v>
+        <v>0.03102206896551724</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.05073157894736842</v>
+        <v>0.03323793103448276</v>
       </c>
       <c r="R1" t="n">
-        <v>0.05411368421052631</v>
+        <v>0.03545379310344828</v>
       </c>
       <c r="S1" t="n">
-        <v>0.05749578947368421</v>
+        <v>0.03766965517241379</v>
       </c>
       <c r="T1" t="n">
-        <v>0.0608778947368421</v>
+        <v>0.03988551724137931</v>
       </c>
       <c r="U1" t="n">
+        <v>0.04210137931034483</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.04431724137931035</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.04653310344827586</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.04874896551724138</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.0509648275862069</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.05318068965517241</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.05539655172413793</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.05761241379310345</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.05982827586206897</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.06204413793103448</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.06426</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01356913183279743</v>
+        <v>0.0694403345548328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01381959722457269</v>
+        <v>0.07028010980520992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01407006261634794</v>
+        <v>0.07111988505558704</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0143205280081232</v>
+        <v>0.07195966030596418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01457099339989846</v>
+        <v>0.07279943555634129</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01482145879167372</v>
+        <v>0.07363921080671842</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01507192418344897</v>
+        <v>0.07447898605709553</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01532238957522423</v>
+        <v>0.07531876130747267</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01557285496699949</v>
+        <v>0.07615853655784979</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01582332035877475</v>
+        <v>0.07699831180822693</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01607378575055001</v>
+        <v>0.07783808705860404</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01632425114232527</v>
+        <v>0.07867786230898118</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01657471653410053</v>
+        <v>0.0795176375593583</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01682518192587578</v>
+        <v>0.08035741280973543</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01707564731765104</v>
+        <v>0.08119718806011254</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0173261127094263</v>
+        <v>0.08203696331048967</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01757657810120156</v>
+        <v>0.0828767385608668</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01782704349297681</v>
+        <v>0.08371651381124393</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01807750888475208</v>
+        <v>0.08455628906162105</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01832797427652733</v>
+        <v>0.08539606431199818</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.08623583956237529</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.08707561481275244</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.08791539006312955</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.08875516531350668</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.0895949405638838</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.09043471581426094</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.09127449106463806</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.09211426631501517</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.09295404156539229</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.09379381681576943</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01356913183279743</v>
+        <v>0.0694403345548328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01381959722457269</v>
+        <v>0.07028010980520992</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01407006261634794</v>
+        <v>0.07111988505558704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0143205280081232</v>
+        <v>0.07195966030596418</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01457099339989846</v>
+        <v>0.07279943555634129</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01482145879167372</v>
+        <v>0.07363921080671842</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01507192418344897</v>
+        <v>0.07447898605709553</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01532238957522423</v>
+        <v>0.07531876130747267</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01557285496699949</v>
+        <v>0.07615853655784979</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01582332035877475</v>
+        <v>0.07699831180822693</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01607378575055001</v>
+        <v>0.07783808705860404</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01632425114232527</v>
+        <v>0.07867786230898118</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01657471653410053</v>
+        <v>0.0795176375593583</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01682518192587578</v>
+        <v>0.08035741280973543</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01707564731765104</v>
+        <v>0.08119718806011254</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0173261127094263</v>
+        <v>0.08203696331048967</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01757657810120156</v>
+        <v>0.0828767385608668</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01782704349297681</v>
+        <v>0.08371651381124393</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01807750888475208</v>
+        <v>0.08455628906162105</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01832797427652733</v>
+        <v>0.08539606431199818</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.08623583956237529</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.08707561481275244</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.08791539006312955</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.08875516531350668</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0895949405638838</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.09043471581426094</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.09127449106463806</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.09211426631501517</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.09295404156539229</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.09379381681576943</v>
       </c>
     </row>
   </sheetData>
